--- a/public/downloads/GauthierFacile2019.xlsx
+++ b/public/downloads/GauthierFacile2019.xlsx
@@ -8,29 +8,31 @@
   </bookViews>
   <sheets>
     <sheet name="MLIP_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="anomaly" sheetId="2" r:id="rId2"/>
-    <sheet name="AlphaNet-v1-OMA" sheetId="3" r:id="rId3"/>
-    <sheet name="CHGNetv0.3.0" sheetId="4" r:id="rId4"/>
-    <sheet name="DPA-3.1-3M-FT" sheetId="5" r:id="rId5"/>
-    <sheet name="Eqnorm-MPtrj" sheetId="6" r:id="rId6"/>
-    <sheet name="eSEN-30M-OAM" sheetId="7" r:id="rId7"/>
-    <sheet name="GRACE-2L-OAM" sheetId="8" r:id="rId8"/>
-    <sheet name="MACE-MPA-0" sheetId="9" r:id="rId9"/>
-    <sheet name="MATLANTISv8" sheetId="10" r:id="rId10"/>
-    <sheet name="MatterSim_v1_5M" sheetId="11" r:id="rId11"/>
-    <sheet name="ORB-v3" sheetId="12" r:id="rId12"/>
-    <sheet name="SevenNet-MF-OMPA" sheetId="13" r:id="rId13"/>
-    <sheet name="UMA-m-1p1_oc20" sheetId="14" r:id="rId14"/>
-    <sheet name="UMA-m-1p1_omat" sheetId="15" r:id="rId15"/>
-    <sheet name="UMA-s-1p1_oc20" sheetId="16" r:id="rId16"/>
-    <sheet name="UMA-s-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="MLIP_Data_shifted" sheetId="2" r:id="rId2"/>
+    <sheet name="anomaly" sheetId="3" r:id="rId3"/>
+    <sheet name="anomaly_shifted" sheetId="4" r:id="rId4"/>
+    <sheet name="AlphaNet-v1-OMA" sheetId="5" r:id="rId5"/>
+    <sheet name="CHGNetv0.3.0" sheetId="6" r:id="rId6"/>
+    <sheet name="DPA-3.1-3M-FT" sheetId="7" r:id="rId7"/>
+    <sheet name="Eqnorm-MPtrj" sheetId="8" r:id="rId8"/>
+    <sheet name="eSEN-30M-OAM" sheetId="9" r:id="rId9"/>
+    <sheet name="GRACE-2L-OAM" sheetId="10" r:id="rId10"/>
+    <sheet name="MACE-MPA-0" sheetId="11" r:id="rId11"/>
+    <sheet name="MATLANTISv8" sheetId="12" r:id="rId12"/>
+    <sheet name="MatterSim_v1_5M" sheetId="13" r:id="rId13"/>
+    <sheet name="ORB-v3" sheetId="14" r:id="rId14"/>
+    <sheet name="SevenNet-MF-OMPA" sheetId="15" r:id="rId15"/>
+    <sheet name="UMA-m-1p1_oc20" sheetId="16" r:id="rId16"/>
+    <sheet name="UMA-m-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="UMA-s-1p1_oc20" sheetId="18" r:id="rId18"/>
+    <sheet name="UMA-s-1p1_omat" sheetId="19" r:id="rId19"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="53">
   <si>
     <t>MLIP_name</t>
   </si>
@@ -62,10 +64,10 @@
     <t>Num_total</t>
   </si>
   <si>
-    <t>Time_total (s)</t>
+    <t>Time_total (ms)</t>
   </si>
   <si>
-    <t>Time_per_step (s)</t>
+    <t>Time_per_step (ms)</t>
   </si>
   <si>
     <t>Steps_total</t>
@@ -165,6 +167,27 @@
   </si>
   <si>
     <t>Adsorbate_name</t>
+  </si>
+  <si>
+    <t>Gas shift correction</t>
+  </si>
+  <si>
+    <t>Shift (eV)</t>
+  </si>
+  <si>
+    <t>N_fit</t>
+  </si>
+  <si>
+    <t>MAE_total_shifted (eV)</t>
+  </si>
+  <si>
+    <t>MAE_normal_shifted (eV)</t>
+  </si>
+  <si>
+    <t>Num_normal_shifted</t>
+  </si>
+  <si>
+    <t>Num_energy_anomaly_shifted</t>
   </si>
   <si>
     <t>CO2</t>
@@ -637,9 +660,7 @@
       <c r="H3" s="4">
         <v>1.022093673876952</v>
       </c>
-      <c r="I3" s="4">
-        <v>0</v>
-      </c>
+      <c r="I3" s="4"/>
       <c r="J3" s="4">
         <v>1.026743789843749</v>
       </c>
@@ -653,10 +674,10 @@
         <v>1</v>
       </c>
       <c r="N3" s="5">
-        <v>21.9549286365509</v>
+        <v>21954.9286365509</v>
       </c>
       <c r="O3" s="4">
-        <v>0.03341693856400442</v>
+        <v>33.41693856400442</v>
       </c>
       <c r="P3" s="5">
         <v>657</v>
@@ -687,9 +708,7 @@
       <c r="H4" s="4">
         <v>0.6044911348144524</v>
       </c>
-      <c r="I4" s="4">
-        <v>0</v>
-      </c>
+      <c r="I4" s="4"/>
       <c r="J4" s="4">
         <v>0.4882039033691399</v>
       </c>
@@ -703,10 +722,10 @@
         <v>1</v>
       </c>
       <c r="N4" s="5">
-        <v>27.74876809120178</v>
+        <v>27748.76809120178</v>
       </c>
       <c r="O4" s="4">
-        <v>0.04834280155261635</v>
+        <v>48.34280155261634</v>
       </c>
       <c r="P4" s="5">
         <v>574</v>
@@ -737,9 +756,7 @@
       <c r="H5" s="4">
         <v>0.565562208823394</v>
       </c>
-      <c r="I5" s="4">
-        <v>0</v>
-      </c>
+      <c r="I5" s="4"/>
       <c r="J5" s="4">
         <v>0.426616823009681</v>
       </c>
@@ -753,10 +770,10 @@
         <v>1</v>
       </c>
       <c r="N5" s="5">
-        <v>225.9359827041626</v>
+        <v>225935.9827041626</v>
       </c>
       <c r="O5" s="4">
-        <v>0.446513799810598</v>
+        <v>446.513799810598</v>
       </c>
       <c r="P5" s="5">
         <v>506</v>
@@ -787,9 +804,7 @@
       <c r="H6" s="4">
         <v>0.6796826326171868</v>
       </c>
-      <c r="I6" s="4">
-        <v>0</v>
-      </c>
+      <c r="I6" s="4"/>
       <c r="J6" s="4">
         <v>0.4606179200927727</v>
       </c>
@@ -803,10 +818,10 @@
         <v>1</v>
       </c>
       <c r="N6" s="5">
-        <v>49.12579083442688</v>
+        <v>49125.79083442688</v>
       </c>
       <c r="O6" s="4">
-        <v>0.1004617399477032</v>
+        <v>100.4617399477032</v>
       </c>
       <c r="P6" s="5">
         <v>489</v>
@@ -837,9 +852,7 @@
       <c r="H7" s="4">
         <v>0.2275933229248039</v>
       </c>
-      <c r="I7" s="4">
-        <v>0</v>
-      </c>
+      <c r="I7" s="4"/>
       <c r="J7" s="4">
         <v>0.1233910524169914</v>
       </c>
@@ -853,10 +866,10 @@
         <v>1</v>
       </c>
       <c r="N7" s="5">
-        <v>86.27722501754761</v>
+        <v>86277.22501754761</v>
       </c>
       <c r="O7" s="4">
-        <v>0.1778911856031909</v>
+        <v>177.891185603191</v>
       </c>
       <c r="P7" s="5">
         <v>485</v>
@@ -887,9 +900,7 @@
       <c r="H8" s="4">
         <v>0.8742022362344528</v>
       </c>
-      <c r="I8" s="4">
-        <v>0</v>
-      </c>
+      <c r="I8" s="4"/>
       <c r="J8" s="4">
         <v>0.6381817827329996</v>
       </c>
@@ -903,10 +914,10 @@
         <v>1</v>
       </c>
       <c r="N8" s="5">
-        <v>4.635547161102295</v>
+        <v>4635.547161102295</v>
       </c>
       <c r="O8" s="4">
-        <v>0.01367418041623096</v>
+        <v>13.67418041623096</v>
       </c>
       <c r="P8" s="5">
         <v>339</v>
@@ -937,9 +948,7 @@
       <c r="H9" s="4">
         <v>0.7002686464111321</v>
       </c>
-      <c r="I9" s="4">
-        <v>0</v>
-      </c>
+      <c r="I9" s="4"/>
       <c r="J9" s="4">
         <v>0.5380333864013664</v>
       </c>
@@ -953,10 +962,10 @@
         <v>1</v>
       </c>
       <c r="N9" s="5">
-        <v>16.12533044815063</v>
+        <v>16125.33044815063</v>
       </c>
       <c r="O9" s="4">
-        <v>0.03199470327014015</v>
+        <v>31.99470327014015</v>
       </c>
       <c r="P9" s="5">
         <v>504</v>
@@ -1003,10 +1012,10 @@
         <v>1</v>
       </c>
       <c r="N10" s="5">
-        <v>26.824214220047</v>
+        <v>26824.214220047</v>
       </c>
       <c r="O10" s="4">
-        <v>0.0982571949452271</v>
+        <v>98.2571949452271</v>
       </c>
       <c r="P10" s="5">
         <v>273</v>
@@ -1037,9 +1046,7 @@
       <c r="H11" s="4">
         <v>0.2627095186035149</v>
       </c>
-      <c r="I11" s="4">
-        <v>0</v>
-      </c>
+      <c r="I11" s="4"/>
       <c r="J11" s="4">
         <v>0.1422108613769524</v>
       </c>
@@ -1053,10 +1060,10 @@
         <v>1</v>
       </c>
       <c r="N11" s="5">
-        <v>20.89531683921814</v>
+        <v>20895.31683921814</v>
       </c>
       <c r="O11" s="4">
-        <v>0.03987655885346973</v>
+        <v>39.87655885346973</v>
       </c>
       <c r="P11" s="5">
         <v>524</v>
@@ -1087,9 +1094,7 @@
       <c r="H12" s="4">
         <v>0.1859539949218743</v>
       </c>
-      <c r="I12" s="4">
-        <v>0</v>
-      </c>
+      <c r="I12" s="4"/>
       <c r="J12" s="4">
         <v>0.07644357316894457</v>
       </c>
@@ -1103,10 +1108,10 @@
         <v>1</v>
       </c>
       <c r="N12" s="5">
-        <v>7.737339973449707</v>
+        <v>7737.339973449707</v>
       </c>
       <c r="O12" s="4">
-        <v>0.01734829590459576</v>
+        <v>17.34829590459575</v>
       </c>
       <c r="P12" s="5">
         <v>446</v>
@@ -1137,9 +1142,7 @@
       <c r="H13" s="4">
         <v>0.771914383105468</v>
       </c>
-      <c r="I13" s="4">
-        <v>0</v>
-      </c>
+      <c r="I13" s="4"/>
       <c r="J13" s="4">
         <v>0.5584820710937493</v>
       </c>
@@ -1153,10 +1156,10 @@
         <v>1</v>
       </c>
       <c r="N13" s="5">
-        <v>37.36857986450195</v>
+        <v>37368.57986450195</v>
       </c>
       <c r="O13" s="4">
-        <v>0.08194864005373236</v>
+        <v>81.94864005373236</v>
       </c>
       <c r="P13" s="5">
         <v>456</v>
@@ -1203,10 +1206,10 @@
         <v>1</v>
       </c>
       <c r="N14" s="5">
-        <v>1.403781652450562</v>
+        <v>1403.781652450562</v>
       </c>
       <c r="O14" s="4">
-        <v>0.2339636087417603</v>
+        <v>233.9636087417603</v>
       </c>
       <c r="P14" s="5">
         <v>6</v>
@@ -1237,9 +1240,7 @@
       <c r="H15" s="4">
         <v>1.202610110572998</v>
       </c>
-      <c r="I15" s="4">
-        <v>0</v>
-      </c>
+      <c r="I15" s="4"/>
       <c r="J15" s="4">
         <v>1.071932336024524</v>
       </c>
@@ -1253,10 +1254,10 @@
         <v>1</v>
       </c>
       <c r="N15" s="5">
-        <v>116.728004693985</v>
+        <v>116728.004693985</v>
       </c>
       <c r="O15" s="4">
-        <v>0.2358141508969394</v>
+        <v>235.8141508969394</v>
       </c>
       <c r="P15" s="5">
         <v>495</v>
@@ -1303,10 +1304,10 @@
         <v>1</v>
       </c>
       <c r="N16" s="5">
-        <v>2.943548679351807</v>
+        <v>2943.548679351807</v>
       </c>
       <c r="O16" s="4">
-        <v>0.09811828931172689</v>
+        <v>98.1182893117269</v>
       </c>
       <c r="P16" s="5">
         <v>30</v>
@@ -1337,9 +1338,7 @@
       <c r="H17" s="4">
         <v>0.561688800982715</v>
       </c>
-      <c r="I17" s="4">
-        <v>0</v>
-      </c>
+      <c r="I17" s="4"/>
       <c r="J17" s="4">
         <v>0.4848387443344322</v>
       </c>
@@ -1353,10 +1352,10 @@
         <v>1</v>
       </c>
       <c r="N17" s="5">
-        <v>38.54163765907288</v>
+        <v>38541.63765907288</v>
       </c>
       <c r="O17" s="4">
-        <v>0.09807032483224651</v>
+        <v>98.07032483224651</v>
       </c>
       <c r="P17" s="5">
         <v>393</v>
@@ -1384,7 +1383,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1395,9 +1394,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1431,8 +1436,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1454,50 +1467,80 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.1205489130500403</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.1205489130500403</v>
-      </c>
+        <v>0.8742022362344528</v>
+      </c>
+      <c r="C3" s="4"/>
       <c r="D3" s="4">
-        <v>0.1183301751108097</v>
+        <v>0.6381817827329996</v>
       </c>
       <c r="E3" s="4">
-        <v>57.24489795918367</v>
+        <v>29.38775510204082</v>
       </c>
       <c r="F3" s="4">
-        <v>71.07382550335571</v>
+        <v>31.40939597315436</v>
       </c>
       <c r="G3" s="5">
         <v>1</v>
       </c>
       <c r="H3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>0</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.8742022362344528</v>
+      </c>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="5">
+        <v>0</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1508,6 +1551,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1515,7 +1559,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1526,9 +1570,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1562,8 +1612,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1585,25 +1643,41 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2627095186035149</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0</v>
-      </c>
+        <v>0.7002686464111321</v>
+      </c>
+      <c r="C3" s="4"/>
       <c r="D3" s="4">
-        <v>0.1422108613769524</v>
+        <v>0.5380333864013664</v>
       </c>
       <c r="E3" s="4">
-        <v>0</v>
+        <v>19.21768707482994</v>
       </c>
       <c r="F3" s="4">
-        <v>17.08053691275168</v>
+        <v>30.13422818791946</v>
       </c>
       <c r="G3" s="5">
         <v>1</v>
@@ -1626,9 +1700,23 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>0</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.7002686464111321</v>
+      </c>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="5">
+        <v>0</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1639,6 +1727,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1646,7 +1735,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1657,9 +1746,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1693,8 +1788,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1716,50 +1819,84 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.1859539949218743</v>
+        <v>0.1205489130500403</v>
       </c>
       <c r="C3" s="4">
-        <v>0</v>
+        <v>0.1205489130500403</v>
       </c>
       <c r="D3" s="4">
-        <v>0.07644357316894457</v>
+        <v>0.1183301751108097</v>
       </c>
       <c r="E3" s="4">
-        <v>25.17006802721091</v>
+        <v>57.24489795918367</v>
       </c>
       <c r="F3" s="4">
-        <v>32.8076062639821</v>
+        <v>71.07382550335571</v>
       </c>
       <c r="G3" s="5">
         <v>1</v>
       </c>
       <c r="H3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>1</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1205489130500403</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1205489130500403</v>
+      </c>
+      <c r="R3" s="5">
+        <v>1</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1770,6 +1907,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1777,7 +1915,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1788,9 +1926,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1824,8 +1968,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1847,25 +1999,41 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.771914383105468</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0</v>
-      </c>
+        <v>0.2627095186035149</v>
+      </c>
+      <c r="C3" s="4"/>
       <c r="D3" s="4">
-        <v>0.5584820710937493</v>
+        <v>0.1422108613769524</v>
       </c>
       <c r="E3" s="4">
-        <v>22.14285714285714</v>
+        <v>0</v>
       </c>
       <c r="F3" s="4">
-        <v>30.1006711409396</v>
+        <v>17.08053691275168</v>
       </c>
       <c r="G3" s="5">
         <v>1</v>
@@ -1888,9 +2056,23 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>0</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2627095186035149</v>
+      </c>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="5">
+        <v>0</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1901,6 +2083,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1908,7 +2091,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1919,9 +2102,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1955,8 +2144,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1978,50 +2175,80 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.1340376340668428</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.1340376340668428</v>
-      </c>
+        <v>0.1859539949218743</v>
+      </c>
+      <c r="C3" s="4"/>
       <c r="D3" s="4">
-        <v>0.1387287580292451</v>
+        <v>0.07644357316894457</v>
       </c>
       <c r="E3" s="4">
-        <v>100</v>
+        <v>25.17006802721091</v>
       </c>
       <c r="F3" s="4">
-        <v>100</v>
+        <v>32.8076062639821</v>
       </c>
       <c r="G3" s="5">
         <v>1</v>
       </c>
       <c r="H3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>0</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1859539949218743</v>
+      </c>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="5">
+        <v>0</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2032,6 +2259,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2039,7 +2267,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2050,9 +2278,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2086,8 +2320,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2109,25 +2351,41 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>1.202610110572998</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0</v>
-      </c>
+        <v>0.771914383105468</v>
+      </c>
+      <c r="C3" s="4"/>
       <c r="D3" s="4">
-        <v>1.071932336024524</v>
+        <v>0.5584820710937493</v>
       </c>
       <c r="E3" s="4">
-        <v>24.59183673469388</v>
+        <v>22.14285714285714</v>
       </c>
       <c r="F3" s="4">
-        <v>32.08053691275168</v>
+        <v>30.1006711409396</v>
       </c>
       <c r="G3" s="5">
         <v>1</v>
@@ -2150,9 +2408,23 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>0</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.771914383105468</v>
+      </c>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="5">
+        <v>0</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2163,6 +2435,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2170,7 +2443,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2181,9 +2454,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2217,8 +2496,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2240,25 +2527,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.06856050126954472</v>
+        <v>0.1340376340668428</v>
       </c>
       <c r="C3" s="4">
-        <v>0.06856050126954472</v>
+        <v>0.1340376340668428</v>
       </c>
       <c r="D3" s="4">
-        <v>0.07031383150014392</v>
+        <v>0.1387287580292451</v>
       </c>
       <c r="E3" s="4">
-        <v>99.59183673469387</v>
+        <v>100</v>
       </c>
       <c r="F3" s="4">
-        <v>99.53020134228188</v>
+        <v>100</v>
       </c>
       <c r="G3" s="5">
         <v>1</v>
@@ -2281,9 +2586,25 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>1</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1340376340668428</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1340376340668428</v>
+      </c>
+      <c r="R3" s="5">
+        <v>1</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2294,6 +2615,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2301,7 +2623,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2312,9 +2634,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2348,8 +2676,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2371,25 +2707,41 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.561688800982715</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0</v>
-      </c>
+        <v>1.202610110572998</v>
+      </c>
+      <c r="C3" s="4"/>
       <c r="D3" s="4">
-        <v>0.4848387443344322</v>
+        <v>1.071932336024524</v>
       </c>
       <c r="E3" s="4">
-        <v>34.89795918367347</v>
+        <v>24.59183673469388</v>
       </c>
       <c r="F3" s="4">
-        <v>40</v>
+        <v>32.08053691275168</v>
       </c>
       <c r="G3" s="5">
         <v>1</v>
@@ -2412,9 +2764,23 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>0</v>
+      </c>
+      <c r="P3" s="4">
+        <v>1.202610110572998</v>
+      </c>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="5">
+        <v>0</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2425,12 +2791,1202 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.06856050126954472</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.06856050126954472</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.07031383150014392</v>
+      </c>
+      <c r="E3" s="4">
+        <v>99.59183673469387</v>
+      </c>
+      <c r="F3" s="4">
+        <v>99.53020134228188</v>
+      </c>
+      <c r="G3" s="5">
+        <v>1</v>
+      </c>
+      <c r="H3" s="5">
+        <v>1</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>1</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.06856050126954472</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.06856050126954472</v>
+      </c>
+      <c r="R3" s="5">
+        <v>1</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.561688800982715</v>
+      </c>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4">
+        <v>0.4848387443344322</v>
+      </c>
+      <c r="E3" s="4">
+        <v>34.89795918367347</v>
+      </c>
+      <c r="F3" s="4">
+        <v>40</v>
+      </c>
+      <c r="G3" s="5">
+        <v>1</v>
+      </c>
+      <c r="H3" s="5">
+        <v>0</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>1</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>1</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>0</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.561688800982715</v>
+      </c>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="5">
+        <v>0</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="10" width="18.7109375" customWidth="1"/>
+    <col min="11" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:16" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3">
+        <v>0</v>
+      </c>
+      <c r="C3" s="3">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3">
+        <v>100</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3">
+        <v>100</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>1.022093673876952</v>
+      </c>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4">
+        <v>1.026743789843749</v>
+      </c>
+      <c r="K3" s="4">
+        <v>7.244897959183674</v>
+      </c>
+      <c r="L3" s="4">
+        <v>5.17897091722595</v>
+      </c>
+      <c r="M3" s="5">
+        <v>1</v>
+      </c>
+      <c r="N3" s="5">
+        <v>21954.9286365509</v>
+      </c>
+      <c r="O3" s="4">
+        <v>33.41693856400442</v>
+      </c>
+      <c r="P3" s="5">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3">
+        <v>100</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3">
+        <v>100</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0.6044911348144524</v>
+      </c>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4">
+        <v>0.4882039033691399</v>
+      </c>
+      <c r="K4" s="4">
+        <v>12.99319727891156</v>
+      </c>
+      <c r="L4" s="4">
+        <v>24.07158836689038</v>
+      </c>
+      <c r="M4" s="5">
+        <v>1</v>
+      </c>
+      <c r="N4" s="5">
+        <v>27748.76809120178</v>
+      </c>
+      <c r="O4" s="4">
+        <v>48.34280155261634</v>
+      </c>
+      <c r="P4" s="5">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3">
+        <v>100</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3">
+        <v>100</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0.565562208823394</v>
+      </c>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4">
+        <v>0.426616823009681</v>
+      </c>
+      <c r="K5" s="4">
+        <v>21.70068027210884</v>
+      </c>
+      <c r="L5" s="4">
+        <v>28.8814317673378</v>
+      </c>
+      <c r="M5" s="5">
+        <v>1</v>
+      </c>
+      <c r="N5" s="5">
+        <v>225935.9827041626</v>
+      </c>
+      <c r="O5" s="4">
+        <v>446.513799810598</v>
+      </c>
+      <c r="P5" s="5">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3">
+        <v>100</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>100</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0.6796826326171868</v>
+      </c>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4">
+        <v>0.4606179200927727</v>
+      </c>
+      <c r="K6" s="4">
+        <v>18.6734693877551</v>
+      </c>
+      <c r="L6" s="4">
+        <v>26.87919463087248</v>
+      </c>
+      <c r="M6" s="5">
+        <v>1</v>
+      </c>
+      <c r="N6" s="5">
+        <v>49125.79083442688</v>
+      </c>
+      <c r="O6" s="4">
+        <v>100.4617399477032</v>
+      </c>
+      <c r="P6" s="5">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="3">
+        <v>0</v>
+      </c>
+      <c r="C7" s="3">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3">
+        <v>100</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3">
+        <v>100</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0.2275933229248039</v>
+      </c>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4">
+        <v>0.1233910524169914</v>
+      </c>
+      <c r="K7" s="4">
+        <v>27.55102040816326</v>
+      </c>
+      <c r="L7" s="4">
+        <v>31.84563758389262</v>
+      </c>
+      <c r="M7" s="5">
+        <v>1</v>
+      </c>
+      <c r="N7" s="5">
+        <v>86277.22501754761</v>
+      </c>
+      <c r="O7" s="4">
+        <v>177.891185603191</v>
+      </c>
+      <c r="P7" s="5">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3">
+        <v>100</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>100</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0.8742022362344528</v>
+      </c>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4">
+        <v>0.6381817827329996</v>
+      </c>
+      <c r="K8" s="4">
+        <v>29.38775510204082</v>
+      </c>
+      <c r="L8" s="4">
+        <v>31.40939597315436</v>
+      </c>
+      <c r="M8" s="5">
+        <v>1</v>
+      </c>
+      <c r="N8" s="5">
+        <v>4635.547161102295</v>
+      </c>
+      <c r="O8" s="4">
+        <v>13.67418041623096</v>
+      </c>
+      <c r="P8" s="5">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3">
+        <v>100</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3">
+        <v>100</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0.7002686464111321</v>
+      </c>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4">
+        <v>0.5380333864013664</v>
+      </c>
+      <c r="K9" s="4">
+        <v>19.21768707482994</v>
+      </c>
+      <c r="L9" s="4">
+        <v>30.13422818791946</v>
+      </c>
+      <c r="M9" s="5">
+        <v>1</v>
+      </c>
+      <c r="N9" s="5">
+        <v>16125.33044815063</v>
+      </c>
+      <c r="O9" s="4">
+        <v>31.99470327014015</v>
+      </c>
+      <c r="P9" s="5">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3">
+        <v>100</v>
+      </c>
+      <c r="C10" s="3">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.1205489130500403</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0.1205489130500403</v>
+      </c>
+      <c r="J10" s="4">
+        <v>0.1183301751108097</v>
+      </c>
+      <c r="K10" s="4">
+        <v>57.24489795918367</v>
+      </c>
+      <c r="L10" s="4">
+        <v>71.07382550335571</v>
+      </c>
+      <c r="M10" s="5">
+        <v>1</v>
+      </c>
+      <c r="N10" s="5">
+        <v>26824.214220047</v>
+      </c>
+      <c r="O10" s="4">
+        <v>98.2571949452271</v>
+      </c>
+      <c r="P10" s="5">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="3">
+        <v>0</v>
+      </c>
+      <c r="C11" s="3">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3">
+        <v>100</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3">
+        <v>100</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4">
+        <v>0.2627095186035149</v>
+      </c>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4">
+        <v>0.1422108613769524</v>
+      </c>
+      <c r="K11" s="4">
+        <v>0</v>
+      </c>
+      <c r="L11" s="4">
+        <v>17.08053691275168</v>
+      </c>
+      <c r="M11" s="5">
+        <v>1</v>
+      </c>
+      <c r="N11" s="5">
+        <v>20895.31683921814</v>
+      </c>
+      <c r="O11" s="4">
+        <v>39.87655885346973</v>
+      </c>
+      <c r="P11" s="5">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="3">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3">
+        <v>100</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3">
+        <v>100</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4">
+        <v>0.1859539949218743</v>
+      </c>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4">
+        <v>0.07644357316894457</v>
+      </c>
+      <c r="K12" s="4">
+        <v>25.17006802721091</v>
+      </c>
+      <c r="L12" s="4">
+        <v>32.8076062639821</v>
+      </c>
+      <c r="M12" s="5">
+        <v>1</v>
+      </c>
+      <c r="N12" s="5">
+        <v>7737.339973449707</v>
+      </c>
+      <c r="O12" s="4">
+        <v>17.34829590459575</v>
+      </c>
+      <c r="P12" s="5">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="3">
+        <v>0</v>
+      </c>
+      <c r="C13" s="3">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3">
+        <v>100</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3">
+        <v>100</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0.771914383105468</v>
+      </c>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4">
+        <v>0.5584820710937493</v>
+      </c>
+      <c r="K13" s="4">
+        <v>22.14285714285714</v>
+      </c>
+      <c r="L13" s="4">
+        <v>30.1006711409396</v>
+      </c>
+      <c r="M13" s="5">
+        <v>1</v>
+      </c>
+      <c r="N13" s="5">
+        <v>37368.57986450195</v>
+      </c>
+      <c r="O13" s="4">
+        <v>81.94864005373236</v>
+      </c>
+      <c r="P13" s="5">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="3">
+        <v>100</v>
+      </c>
+      <c r="C14" s="3">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
+        <v>0.1340376340668428</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0.1340376340668428</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0.1387287580292451</v>
+      </c>
+      <c r="K14" s="4">
+        <v>100</v>
+      </c>
+      <c r="L14" s="4">
+        <v>100</v>
+      </c>
+      <c r="M14" s="5">
+        <v>1</v>
+      </c>
+      <c r="N14" s="5">
+        <v>1403.781652450562</v>
+      </c>
+      <c r="O14" s="4">
+        <v>233.9636087417603</v>
+      </c>
+      <c r="P14" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="3">
+        <v>0</v>
+      </c>
+      <c r="C15" s="3">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3">
+        <v>100</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>100</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <v>1.202610110572998</v>
+      </c>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4">
+        <v>1.071932336024524</v>
+      </c>
+      <c r="K15" s="4">
+        <v>24.59183673469388</v>
+      </c>
+      <c r="L15" s="4">
+        <v>32.08053691275168</v>
+      </c>
+      <c r="M15" s="5">
+        <v>1</v>
+      </c>
+      <c r="N15" s="5">
+        <v>116728.004693985</v>
+      </c>
+      <c r="O15" s="4">
+        <v>235.8141508969394</v>
+      </c>
+      <c r="P15" s="5">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="3">
+        <v>100</v>
+      </c>
+      <c r="C16" s="3">
+        <v>0</v>
+      </c>
+      <c r="D16" s="3">
+        <v>0</v>
+      </c>
+      <c r="E16" s="3">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3">
+        <v>0</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0.06856050126954472</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0.06856050126954472</v>
+      </c>
+      <c r="J16" s="4">
+        <v>0.07031383150014392</v>
+      </c>
+      <c r="K16" s="4">
+        <v>99.59183673469387</v>
+      </c>
+      <c r="L16" s="4">
+        <v>99.53020134228188</v>
+      </c>
+      <c r="M16" s="5">
+        <v>1</v>
+      </c>
+      <c r="N16" s="5">
+        <v>2943.548679351807</v>
+      </c>
+      <c r="O16" s="4">
+        <v>98.1182893117269</v>
+      </c>
+      <c r="P16" s="5">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="3">
+        <v>0</v>
+      </c>
+      <c r="C17" s="3">
+        <v>0</v>
+      </c>
+      <c r="D17" s="3">
+        <v>100</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3">
+        <v>100</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4">
+        <v>0.561688800982715</v>
+      </c>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4">
+        <v>0.4848387443344322</v>
+      </c>
+      <c r="K17" s="4">
+        <v>34.89795918367347</v>
+      </c>
+      <c r="L17" s="4">
+        <v>40</v>
+      </c>
+      <c r="M17" s="5">
+        <v>1</v>
+      </c>
+      <c r="N17" s="5">
+        <v>38541.63765907288</v>
+      </c>
+      <c r="O17" s="4">
+        <v>98.07032483224651</v>
+      </c>
+      <c r="P17" s="5">
+        <v>393</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3185,9 +4741,764 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:N17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="14" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="5">
+        <v>0</v>
+      </c>
+      <c r="C3" s="5">
+        <v>0</v>
+      </c>
+      <c r="D3" s="5">
+        <v>1</v>
+      </c>
+      <c r="E3" s="5">
+        <v>0</v>
+      </c>
+      <c r="F3" s="5">
+        <v>1</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5">
+        <v>0</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>1</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="5">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5">
+        <v>0</v>
+      </c>
+      <c r="D4" s="5">
+        <v>1</v>
+      </c>
+      <c r="E4" s="5">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5">
+        <v>1</v>
+      </c>
+      <c r="G4" s="5">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>1</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5">
+        <v>0</v>
+      </c>
+      <c r="C5" s="5">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5">
+        <v>1</v>
+      </c>
+      <c r="E5" s="5">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5">
+        <v>1</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>1</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="5">
+        <v>0</v>
+      </c>
+      <c r="C6" s="5">
+        <v>0</v>
+      </c>
+      <c r="D6" s="5">
+        <v>1</v>
+      </c>
+      <c r="E6" s="5">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5">
+        <v>1</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>1</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5">
+        <v>0</v>
+      </c>
+      <c r="C7" s="5">
+        <v>0</v>
+      </c>
+      <c r="D7" s="5">
+        <v>1</v>
+      </c>
+      <c r="E7" s="5">
+        <v>0</v>
+      </c>
+      <c r="F7" s="5">
+        <v>1</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>1</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="5">
+        <v>0</v>
+      </c>
+      <c r="C8" s="5">
+        <v>0</v>
+      </c>
+      <c r="D8" s="5">
+        <v>1</v>
+      </c>
+      <c r="E8" s="5">
+        <v>0</v>
+      </c>
+      <c r="F8" s="5">
+        <v>1</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5">
+        <v>1</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="5">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5">
+        <v>0</v>
+      </c>
+      <c r="D9" s="5">
+        <v>1</v>
+      </c>
+      <c r="E9" s="5">
+        <v>0</v>
+      </c>
+      <c r="F9" s="5">
+        <v>1</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5">
+        <v>0</v>
+      </c>
+      <c r="I9" s="5">
+        <v>0</v>
+      </c>
+      <c r="J9" s="5">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5">
+        <v>1</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="5">
+        <v>1</v>
+      </c>
+      <c r="C10" s="5">
+        <v>0</v>
+      </c>
+      <c r="D10" s="5">
+        <v>0</v>
+      </c>
+      <c r="E10" s="5">
+        <v>0</v>
+      </c>
+      <c r="F10" s="5">
+        <v>0</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5">
+        <v>0</v>
+      </c>
+      <c r="I10" s="5">
+        <v>0</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5">
+        <v>0</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="5">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5">
+        <v>0</v>
+      </c>
+      <c r="D11" s="5">
+        <v>1</v>
+      </c>
+      <c r="E11" s="5">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5">
+        <v>1</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5">
+        <v>0</v>
+      </c>
+      <c r="I11" s="5">
+        <v>0</v>
+      </c>
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5">
+        <v>1</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="5">
+        <v>0</v>
+      </c>
+      <c r="C12" s="5">
+        <v>0</v>
+      </c>
+      <c r="D12" s="5">
+        <v>1</v>
+      </c>
+      <c r="E12" s="5">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5">
+        <v>1</v>
+      </c>
+      <c r="G12" s="5">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5">
+        <v>0</v>
+      </c>
+      <c r="I12" s="5">
+        <v>0</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5">
+        <v>1</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="5">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5">
+        <v>0</v>
+      </c>
+      <c r="D13" s="5">
+        <v>1</v>
+      </c>
+      <c r="E13" s="5">
+        <v>0</v>
+      </c>
+      <c r="F13" s="5">
+        <v>1</v>
+      </c>
+      <c r="G13" s="5">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5">
+        <v>0</v>
+      </c>
+      <c r="I13" s="5">
+        <v>0</v>
+      </c>
+      <c r="J13" s="5">
+        <v>0</v>
+      </c>
+      <c r="K13" s="5">
+        <v>0</v>
+      </c>
+      <c r="L13" s="5">
+        <v>1</v>
+      </c>
+      <c r="M13" s="5">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="5">
+        <v>1</v>
+      </c>
+      <c r="C14" s="5">
+        <v>0</v>
+      </c>
+      <c r="D14" s="5">
+        <v>0</v>
+      </c>
+      <c r="E14" s="5">
+        <v>0</v>
+      </c>
+      <c r="F14" s="5">
+        <v>0</v>
+      </c>
+      <c r="G14" s="5">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5">
+        <v>0</v>
+      </c>
+      <c r="I14" s="5">
+        <v>0</v>
+      </c>
+      <c r="J14" s="5">
+        <v>0</v>
+      </c>
+      <c r="K14" s="5">
+        <v>0</v>
+      </c>
+      <c r="L14" s="5">
+        <v>0</v>
+      </c>
+      <c r="M14" s="5">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="5">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5">
+        <v>0</v>
+      </c>
+      <c r="D15" s="5">
+        <v>1</v>
+      </c>
+      <c r="E15" s="5">
+        <v>0</v>
+      </c>
+      <c r="F15" s="5">
+        <v>1</v>
+      </c>
+      <c r="G15" s="5">
+        <v>0</v>
+      </c>
+      <c r="H15" s="5">
+        <v>0</v>
+      </c>
+      <c r="I15" s="5">
+        <v>0</v>
+      </c>
+      <c r="J15" s="5">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5">
+        <v>0</v>
+      </c>
+      <c r="L15" s="5">
+        <v>1</v>
+      </c>
+      <c r="M15" s="5">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="5">
+        <v>1</v>
+      </c>
+      <c r="C16" s="5">
+        <v>0</v>
+      </c>
+      <c r="D16" s="5">
+        <v>0</v>
+      </c>
+      <c r="E16" s="5">
+        <v>0</v>
+      </c>
+      <c r="F16" s="5">
+        <v>0</v>
+      </c>
+      <c r="G16" s="5">
+        <v>0</v>
+      </c>
+      <c r="H16" s="5">
+        <v>0</v>
+      </c>
+      <c r="I16" s="5">
+        <v>0</v>
+      </c>
+      <c r="J16" s="5">
+        <v>0</v>
+      </c>
+      <c r="K16" s="5">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5">
+        <v>0</v>
+      </c>
+      <c r="M16" s="5">
+        <v>0</v>
+      </c>
+      <c r="N16" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="5">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5">
+        <v>0</v>
+      </c>
+      <c r="D17" s="5">
+        <v>1</v>
+      </c>
+      <c r="E17" s="5">
+        <v>0</v>
+      </c>
+      <c r="F17" s="5">
+        <v>1</v>
+      </c>
+      <c r="G17" s="5">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5">
+        <v>0</v>
+      </c>
+      <c r="I17" s="5">
+        <v>0</v>
+      </c>
+      <c r="J17" s="5">
+        <v>0</v>
+      </c>
+      <c r="K17" s="5">
+        <v>0</v>
+      </c>
+      <c r="L17" s="5">
+        <v>1</v>
+      </c>
+      <c r="M17" s="5">
+        <v>0</v>
+      </c>
+      <c r="N17" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3198,9 +5509,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3234,8 +5551,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3257,17 +5582,33 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>1.022093673876952</v>
       </c>
-      <c r="C3" s="4">
-        <v>0</v>
-      </c>
+      <c r="C3" s="4"/>
       <c r="D3" s="4">
         <v>1.026743789843749</v>
       </c>
@@ -3298,9 +5639,23 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>0</v>
+      </c>
+      <c r="P3" s="4">
+        <v>1.022093673876952</v>
+      </c>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="5">
+        <v>0</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3311,14 +5666,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3329,9 +5685,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3365,8 +5727,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3388,17 +5758,33 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.6044911348144524</v>
       </c>
-      <c r="C3" s="4">
-        <v>0</v>
-      </c>
+      <c r="C3" s="4"/>
       <c r="D3" s="4">
         <v>0.4882039033691399</v>
       </c>
@@ -3429,9 +5815,23 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>0</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.6044911348144524</v>
+      </c>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="5">
+        <v>0</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3442,14 +5842,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3460,9 +5861,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3496,8 +5903,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3519,17 +5934,33 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.565562208823394</v>
       </c>
-      <c r="C3" s="4">
-        <v>0</v>
-      </c>
+      <c r="C3" s="4"/>
       <c r="D3" s="4">
         <v>0.426616823009681</v>
       </c>
@@ -3560,9 +5991,23 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>0</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.565562208823394</v>
+      </c>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="5">
+        <v>0</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3573,14 +6018,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3591,9 +6037,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3627,8 +6079,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3650,17 +6110,33 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.6796826326171868</v>
       </c>
-      <c r="C3" s="4">
-        <v>0</v>
-      </c>
+      <c r="C3" s="4"/>
       <c r="D3" s="4">
         <v>0.4606179200927727</v>
       </c>
@@ -3691,9 +6167,23 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>0</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.6796826326171868</v>
+      </c>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="5">
+        <v>0</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3704,14 +6194,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3722,9 +6213,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3758,8 +6255,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3781,17 +6286,33 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.2275933229248039</v>
       </c>
-      <c r="C3" s="4">
-        <v>0</v>
-      </c>
+      <c r="C3" s="4"/>
       <c r="D3" s="4">
         <v>0.1233910524169914</v>
       </c>
@@ -3822,9 +6343,23 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>0</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2275933229248039</v>
+      </c>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="5">
+        <v>0</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3835,268 +6370,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.8742022362344528</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.6381817827329996</v>
-      </c>
-      <c r="E3" s="4">
-        <v>29.38775510204082</v>
-      </c>
-      <c r="F3" s="4">
-        <v>31.40939597315436</v>
-      </c>
-      <c r="G3" s="5">
-        <v>1</v>
-      </c>
-      <c r="H3" s="5">
-        <v>0</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>1</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>1</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.7002686464111321</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.5380333864013664</v>
-      </c>
-      <c r="E3" s="4">
-        <v>19.21768707482994</v>
-      </c>
-      <c r="F3" s="4">
-        <v>30.13422818791946</v>
-      </c>
-      <c r="G3" s="5">
-        <v>1</v>
-      </c>
-      <c r="H3" s="5">
-        <v>0</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>1</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>1</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
